--- a/docs/Abu-Twins-Current-Stock-Template.xlsx
+++ b/docs/Abu-Twins-Current-Stock-Template.xlsx
@@ -5,21 +5,23 @@
   <sheets>
     <sheet name="Read me first" sheetId="1" r:id="rId1"/>
     <sheet name="Items" sheetId="2" r:id="rId2"/>
-    <sheet name="Phones in shop" sheetId="3" r:id="rId3"/>
-    <sheet name="Pieces in shop" sheetId="4" r:id="rId4"/>
-    <sheet name="Staff" sheetId="5" r:id="rId5"/>
-    <sheet name="Suppliers" sheetId="6" r:id="rId6"/>
-    <sheet name="Coming goods" sheetId="7" r:id="rId7"/>
-    <sheet name="Allowed words" sheetId="8" r:id="rId8"/>
+    <sheet name="Pieces in shop" sheetId="3" r:id="rId3"/>
+    <sheet name="Phones in shop" sheetId="4" r:id="rId4"/>
+    <sheet name="Customers" sheetId="5" r:id="rId5"/>
+    <sheet name="Staff" sheetId="6" r:id="rId6"/>
+    <sheet name="Suppliers" sheetId="7" r:id="rId7"/>
+    <sheet name="Coming goods" sheetId="8" r:id="rId8"/>
+    <sheet name="Allowed words" sheetId="9" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1">'Items'!A1:O7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2">'Phones in shop'!A1:L6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3">'Pieces in shop'!A1:F4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4">'Staff'!A1:F5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5">'Suppliers'!A1:H3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6">'Coming goods'!A1:K4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7">'Allowed words'!A1:C28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2">'Pieces in shop'!A1:F5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3">'Phones in shop'!A1:L7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4">'Customers'!A1:H4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5">'Staff'!A1:F7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6">'Suppliers'!A1:H3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7">'Coming goods'!A1:K4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8">'Allowed words'!A1:C31</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -413,7 +415,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B36"/>
+  <dimension ref="A1:B40"/>
   <cols>
     <col min="1" max="1" width="28.83203125" customWidth="1"/>
     <col min="2" max="2" width="88.83203125" customWidth="1"/>
@@ -426,7 +428,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Prepared by Techvaults Limited  ·  techvaults.com  ·  8 September 2026</v>
+        <v>Prepared by Techvaults Limited  ·  techvaults.com  ·  9 September 2026</v>
       </c>
     </row>
     <row r="3">
@@ -441,7 +443,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Fill this workbook with what is on the shelf tonight at Iwo Road and Challenge. Send the filled file back. We load it so staff can sell and you can test the real workflows.</v>
+        <v>Fill this workbook with what is on the shelf tonight at Iwo Road, Bodija, and Challenge. Send the filled file back, or load it yourself on the Upload stock screen. Either way staff can then sell and you can test the real workflows.</v>
       </c>
     </row>
     <row r="6">
@@ -461,7 +463,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>2. Use the exact shop names: Iwo Road, Ibadan    and    Challenge, Ibadan</v>
+        <v>2. Use the exact shop names: Iwo Road, Ibadan    Bodija, Ibadan    Challenge, Ibadan. The short codes IWO, BOD, and CHL also work.</v>
       </c>
     </row>
     <row r="10">
@@ -481,157 +483,180 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v/>
+        <v>6. The tabs load in this order: Items first, then Pieces in shop, then Phones in shop, then Customers. Nothing can be counted or booked in until Items is loaded.</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Tabs you must fill for tomorrow</v>
+        <v>7. Do not rename the column headings. They are what the shop system reads.</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Items</v>
-      </c>
-      <c r="B15" t="str">
-        <v>The list of things you sell. One row per model, not per box. This does not put stock on the shelf.</v>
+        <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Phones in shop</v>
-      </c>
-      <c r="B16" t="str">
-        <v>One row for every phone, tablet, or serial item sitting in a shop tonight. IMEI 1 must be the number on the box, at least 14 digits.</v>
+        <v>Tabs you must fill for tomorrow</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Pieces in shop</v>
+        <v>Items</v>
       </c>
       <c r="B17" t="str">
-        <v>Cords, chargers, and other goods with no unique number. One row per item per shop, with the piece count.</v>
+        <v>The list of things you sell. One row per model, not per box. This does not put stock on the shelf.</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Staff</v>
+        <v>Phones in shop</v>
       </c>
       <c r="B18" t="str">
-        <v>People who will sign in. Job and shop decide what they see.</v>
+        <v>One row for every phone, tablet, or serial item sitting in a shop tonight. IMEI 1 must be the number on the box, at least 14 digits.</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v/>
+        <v>Pieces in shop</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Cords, chargers, and other goods with no unique number. One row per item per shop, with the piece count.</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Tabs that help, but do not block a first live sale</v>
+        <v>Customers</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Named buyers, so old debts, warranties, and returns can be attached to the right person. Optional for a first sale.</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Suppliers</v>
+        <v>Staff</v>
       </c>
       <c r="B21" t="str">
-        <v>Who you buy from.</v>
+        <v>People who will sign in. Job and shop decide what they see.</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Coming goods</v>
-      </c>
-      <c r="B22" t="str">
-        <v>Cartons still on the road. Do not mix these with Phones in shop.</v>
+        <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Allowed words</v>
-      </c>
-      <c r="B23" t="str">
-        <v>The only values we can read for shop, tracking, condition, and job.</v>
+        <v>Tabs that help, but do not block a first live sale</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v/>
+        <v>Suppliers</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Who you buy from.</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Tracking</v>
+        <v>Coming goods</v>
+      </c>
+      <c r="B25" t="str">
+        <v>Cartons still on the road. Do not mix these with Phones in shop.</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>IMEI</v>
+        <v>Allowed words</v>
       </c>
       <c r="B26" t="str">
-        <v>Phones. Every unit needs IMEI 1.</v>
+        <v>The only values we can read for shop, tracking, condition, and job.</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>SERIAL</v>
-      </c>
-      <c r="B27" t="str">
-        <v>Buds, some tablets. Every unit needs a serial.</v>
+        <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>NONE</v>
-      </c>
-      <c r="B28" t="str">
-        <v>Cords and chargers. Count pieces. No IMEI.</v>
+        <v>Tracking</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v/>
+        <v>IMEI</v>
+      </c>
+      <c r="B29" t="str">
+        <v>Phones. Every unit needs IMEI 1.</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>What not to send</v>
+        <v>SERIAL</v>
+      </c>
+      <c r="B30" t="str">
+        <v>Buds, some tablets. Every unit needs a serial.</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Do not type a new IMEI because the box is missing. Leave that unit off the list until you find the number.</v>
+        <v>NONE</v>
+      </c>
+      <c r="B31" t="str">
+        <v>Cords and chargers. Count pieces. No IMEI.</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Do not send old paper invoices to be rewritten as history. Tomorrow starts from what is on the shelf now.</v>
+        <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Do not invent a buyer so a credit sale can be tested. Use a real named customer later, or a walk-in with no name.</v>
+        <v>What not to send</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v/>
+        <v>Do not type a new IMEI because the box is missing. Leave that unit off the list until you find the number.</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>When you are done</v>
+        <v>Do not send old paper invoices to be rewritten as history. Tomorrow starts from what is on the shelf now.</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Save this Excel. Send it back to Techvaults with the message that Iwo Road and Challenge were counted tonight. We will load names, IMEIs, and piece counts, then tell you when Sell now is ready.</v>
+        <v>Do not invent a buyer so a credit sale can be tested. Use a real named customer later, or a walk-in with no name.</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>When you are done</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>Save this Excel. Either send it back to Techvaults, or sign in as the Stock uploader and load it yourself on Upload stock, working down the four steps in order.</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>The shop system checks a whole tab before it saves any of it. If one line is wrong, nothing is loaded and you are told exactly which lines to fix. Sending the same tab twice is safe.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B36"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B40"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -692,7 +717,7 @@
         <v>cost</v>
       </c>
       <c r="L1" t="str">
-        <v>lowest_price</v>
+        <v>minimum_price</v>
       </c>
       <c r="M1" t="str">
         <v>selling_price</v>
@@ -996,7 +1021,127 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:F5"/>
+  <cols>
+    <col min="1" max="1" width="12.83203125" customWidth="1"/>
+    <col min="2" max="2" width="22.83203125" customWidth="1"/>
+    <col min="3" max="3" width="16.83203125" customWidth="1"/>
+    <col min="4" max="4" width="24.83203125" customWidth="1"/>
+    <col min="5" max="5" width="18.83203125" customWidth="1"/>
+    <col min="6" max="6" width="48.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>row_type</v>
+      </c>
+      <c r="B1" t="str">
+        <v>shop</v>
+      </c>
+      <c r="C1" t="str">
+        <v>item_code</v>
+      </c>
+      <c r="D1" t="str">
+        <v>name</v>
+      </c>
+      <c r="E1" t="str">
+        <v>quantity</v>
+      </c>
+      <c r="F1" t="str">
+        <v>notes</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>SAMPLE</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Iwo Road, Ibadan</v>
+      </c>
+      <c r="C2" t="str">
+        <v>CORD-TYPEC</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Type-C charger cord</v>
+      </c>
+      <c r="E2" t="str">
+        <v>20</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Delete this sample. Count the drawer tonight.</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>SAMPLE</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Bodija, Ibadan</v>
+      </c>
+      <c r="C3" t="str">
+        <v>CORD-TYPEC</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Type-C charger cord</v>
+      </c>
+      <c r="E3" t="str">
+        <v>8</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Same item, different shop, different count.</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>SAMPLE</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Challenge, Ibadan</v>
+      </c>
+      <c r="C4" t="str">
+        <v>CORD-TYPEC</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Type-C charger cord</v>
+      </c>
+      <c r="E4" t="str">
+        <v>12</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Count each shop separately.</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>REAL</v>
+      </c>
+      <c r="B5" t="str">
+        <v/>
+      </c>
+      <c r="C5" t="str">
+        <v/>
+      </c>
+      <c r="D5" t="str">
+        <v/>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v>Replace this row. One row per no-number item per shop. tracking on Items must be NONE.</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F5"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:F5"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:L7"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="22.83203125" customWidth="1"/>
@@ -1131,7 +1276,7 @@
         <v>SAMPLE</v>
       </c>
       <c r="B4" t="str">
-        <v>Challenge, Ibadan</v>
+        <v>Bodija, Ibadan</v>
       </c>
       <c r="C4" t="str">
         <v>S24-256-GRY</v>
@@ -1161,7 +1306,7 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>This phone sits at Challenge, not Iwo Road.</v>
+        <v>This phone sits at Bodija, not Iwo Road.</v>
       </c>
     </row>
     <row r="5">
@@ -1169,22 +1314,22 @@
         <v>SAMPLE</v>
       </c>
       <c r="B5" t="str">
-        <v>Iwo Road, Ibadan</v>
+        <v>Challenge, Ibadan</v>
       </c>
       <c r="C5" t="str">
-        <v>BUDS3-WHT</v>
+        <v>S24-256-GRY</v>
       </c>
       <c r="D5" t="str">
-        <v>Galaxy Buds3</v>
+        <v>Galaxy S24 256GB</v>
       </c>
       <c r="E5" t="str">
-        <v/>
+        <v>990000044444444</v>
       </c>
       <c r="F5" t="str">
         <v/>
       </c>
       <c r="G5" t="str">
-        <v>SN-SAMPLE-BUDS-001</v>
+        <v/>
       </c>
       <c r="H5" t="str">
         <v>Brand new</v>
@@ -1193,27 +1338,27 @@
         <v>A</v>
       </c>
       <c r="J5" t="str">
-        <v/>
+        <v>100</v>
       </c>
       <c r="K5" t="str">
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Serial item. Put the serial here. IMEI 1 can stay empty.</v>
+        <v>Same model, third shop. One row per physical phone.</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>REAL</v>
+        <v>SAMPLE</v>
       </c>
       <c r="B6" t="str">
         <v>Iwo Road, Ibadan</v>
       </c>
       <c r="C6" t="str">
-        <v/>
+        <v>BUDS3-WHT</v>
       </c>
       <c r="D6" t="str">
-        <v/>
+        <v>Galaxy Buds3</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -1222,13 +1367,13 @@
         <v/>
       </c>
       <c r="G6" t="str">
-        <v/>
+        <v>SN-SAMPLE-BUDS-001</v>
       </c>
       <c r="H6" t="str">
-        <v/>
+        <v>Brand new</v>
       </c>
       <c r="I6" t="str">
-        <v/>
+        <v>A</v>
       </c>
       <c r="J6" t="str">
         <v/>
@@ -1237,120 +1382,184 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Add one row per phone or serial item on the shelf. Shop must be Iwo Road, Ibadan or Challenge, Ibadan.</v>
+        <v>Serial item. Put the serial here. IMEI 1 can stay empty.</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>REAL</v>
+      </c>
+      <c r="B7" t="str">
+        <v/>
+      </c>
+      <c r="C7" t="str">
+        <v/>
+      </c>
+      <c r="D7" t="str">
+        <v/>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v/>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>Replace this row. One row per phone or serial item on the shelf. Shop must be Iwo Road, Ibadan, Bodija, Ibadan, or Challenge, Ibadan.</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L6"/>
+  <autoFilter ref="A1:L7"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L6"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F4"/>
-  <cols>
-    <col min="1" max="1" width="12.83203125" customWidth="1"/>
-    <col min="2" max="2" width="22.83203125" customWidth="1"/>
-    <col min="3" max="3" width="16.83203125" customWidth="1"/>
-    <col min="4" max="4" width="24.83203125" customWidth="1"/>
-    <col min="5" max="5" width="18.83203125" customWidth="1"/>
-    <col min="6" max="6" width="48.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>row_type</v>
-      </c>
-      <c r="B1" t="str">
-        <v>shop</v>
-      </c>
-      <c r="C1" t="str">
-        <v>item_code</v>
-      </c>
-      <c r="D1" t="str">
-        <v>name</v>
-      </c>
-      <c r="E1" t="str">
-        <v>pieces_on_shelf</v>
-      </c>
-      <c r="F1" t="str">
-        <v>notes</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>SAMPLE</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Iwo Road, Ibadan</v>
-      </c>
-      <c r="C2" t="str">
-        <v>CORD-TYPEC</v>
-      </c>
-      <c r="D2" t="str">
-        <v>Type-C charger cord</v>
-      </c>
-      <c r="E2" t="str">
-        <v>20</v>
-      </c>
-      <c r="F2" t="str">
-        <v>Delete this sample. Count the drawer tonight.</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>SAMPLE</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Challenge, Ibadan</v>
-      </c>
-      <c r="C3" t="str">
-        <v>CORD-TYPEC</v>
-      </c>
-      <c r="D3" t="str">
-        <v>Type-C charger cord</v>
-      </c>
-      <c r="E3" t="str">
-        <v>8</v>
-      </c>
-      <c r="F3" t="str">
-        <v>Same item, different shop, different count.</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>REAL</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Iwo Road, Ibadan</v>
-      </c>
-      <c r="C4" t="str">
-        <v/>
-      </c>
-      <c r="D4" t="str">
-        <v/>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v>One row per no-number item per shop. tracking on Items must be NONE.</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:F4"/>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L7"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:H4"/>
+  <cols>
+    <col min="1" max="1" width="12.83203125" customWidth="1"/>
+    <col min="2" max="2" width="26.83203125" customWidth="1"/>
+    <col min="3" max="3" width="16.83203125" customWidth="1"/>
+    <col min="4" max="4" width="20.83203125" customWidth="1"/>
+    <col min="5" max="5" width="26.83203125" customWidth="1"/>
+    <col min="6" max="6" width="24.83203125" customWidth="1"/>
+    <col min="7" max="7" width="14.83203125" customWidth="1"/>
+    <col min="8" max="8" width="56.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>row_type</v>
+      </c>
+      <c r="B1" t="str">
+        <v>name</v>
+      </c>
+      <c r="C1" t="str">
+        <v>phone</v>
+      </c>
+      <c r="D1" t="str">
+        <v>shop</v>
+      </c>
+      <c r="E1" t="str">
+        <v>email</v>
+      </c>
+      <c r="F1" t="str">
+        <v>address</v>
+      </c>
+      <c r="G1" t="str">
+        <v>credit_limit</v>
+      </c>
+      <c r="H1" t="str">
+        <v>notes</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>SAMPLE</v>
+      </c>
+      <c r="B2" t="str">
+        <v>SAMPLE Chidi Okeke</v>
+      </c>
+      <c r="C2" t="str">
+        <v>08031234567</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Iwo Road, Ibadan</v>
+      </c>
+      <c r="E2" t="str">
+        <v/>
+      </c>
+      <c r="F2" t="str">
+        <v>Bodija, Ibadan</v>
+      </c>
+      <c r="G2" t="str">
+        <v>250000</v>
+      </c>
+      <c r="H2" t="str">
+        <v>Delete this sample. Phone number must be unique across the business.</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>SAMPLE</v>
+      </c>
+      <c r="B3" t="str">
+        <v>SAMPLE Emeka Wholesale</v>
+      </c>
+      <c r="C3" t="str">
+        <v>08039876543</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Bodija, Ibadan</v>
+      </c>
+      <c r="E3" t="str">
+        <v>emeka@example.com</v>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v>1500000</v>
+      </c>
+      <c r="H3" t="str">
+        <v>A trade buyer. credit_limit is how much they may owe at once.</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>REAL</v>
+      </c>
+      <c r="B4" t="str">
+        <v/>
+      </c>
+      <c r="C4" t="str">
+        <v/>
+      </c>
+      <c r="D4" t="str">
+        <v/>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v>Only named buyers you actually know. Leave credit_limit empty or 0 for a customer who always pays in full.</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:H4"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:H4"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F7"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="28.83203125" customWidth="1"/>
@@ -1405,16 +1614,16 @@
         <v>SAMPLE</v>
       </c>
       <c r="B3" t="str">
-        <v>SAMPLE Manager Challenge</v>
+        <v>SAMPLE Manager Bodija</v>
       </c>
       <c r="C3" t="str">
-        <v>manager.challenge@example.com</v>
+        <v>manager.bodija@example.com</v>
       </c>
       <c r="D3" t="str">
         <v>Shop manager</v>
       </c>
       <c r="E3" t="str">
-        <v>Challenge, Ibadan</v>
+        <v>Bodija, Ibadan</v>
       </c>
       <c r="F3" t="str">
         <v>Delete this sample.</v>
@@ -1425,50 +1634,90 @@
         <v>SAMPLE</v>
       </c>
       <c r="B4" t="str">
-        <v>SAMPLE Accountant</v>
+        <v>SAMPLE Manager Challenge</v>
       </c>
       <c r="C4" t="str">
-        <v>accounts@example.com</v>
+        <v>manager.challenge@example.com</v>
       </c>
       <c r="D4" t="str">
-        <v>Accountant</v>
+        <v>Shop manager</v>
       </c>
       <c r="E4" t="str">
-        <v/>
+        <v>Challenge, Ibadan</v>
       </c>
       <c r="F4" t="str">
-        <v>Leave shop empty if this person sees both shops.</v>
+        <v>Delete this sample.</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
+        <v>SAMPLE</v>
+      </c>
+      <c r="B5" t="str">
+        <v>SAMPLE Stock uploader</v>
+      </c>
+      <c r="C5" t="str">
+        <v>uploader@example.com</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Stock uploader</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v>Loads this workbook into the system. Leave shop empty. This job cannot sell or see money.</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>SAMPLE</v>
+      </c>
+      <c r="B6" t="str">
+        <v>SAMPLE Accountant</v>
+      </c>
+      <c r="C6" t="str">
+        <v>accounts@example.com</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Accountant</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v>Leave shop empty if this person sees every shop.</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
         <v>REAL</v>
       </c>
-      <c r="B5" t="str">
-        <v/>
-      </c>
-      <c r="C5" t="str">
-        <v/>
-      </c>
-      <c r="D5" t="str">
-        <v/>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
+      <c r="B7" t="str">
+        <v/>
+      </c>
+      <c r="C7" t="str">
+        <v/>
+      </c>
+      <c r="D7" t="str">
+        <v/>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
         <v>Use a work email they will actually sign in with. Allowed jobs are on Allowed words.</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F5"/>
+  <autoFilter ref="A1:F7"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F7"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H3"/>
   <cols>
@@ -1568,7 +1817,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:K4"/>
   <cols>
@@ -1695,7 +1944,7 @@
         <v>REAL</v>
       </c>
       <c r="B4" t="str">
-        <v>Iwo Road, Ibadan</v>
+        <v/>
       </c>
       <c r="C4" t="str">
         <v/>
@@ -1722,7 +1971,7 @@
         <v/>
       </c>
       <c r="K4" t="str">
-        <v>Only goods that have not arrived. Phones already in the drawer go on Phones in shop instead.</v>
+        <v>Replace this row. Only goods that have not arrived. Phones already in the drawer go on Phones in shop instead.</v>
       </c>
     </row>
   </sheetData>
@@ -1733,9 +1982,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C31"/>
   <cols>
     <col min="1" max="1" width="16.83203125" customWidth="1"/>
     <col min="2" max="2" width="24.83203125" customWidth="1"/>
@@ -1761,7 +2010,7 @@
         <v>Iwo Road, Ibadan</v>
       </c>
       <c r="C2" t="str">
-        <v>Phones in shop, Pieces in shop, Staff, Coming goods</v>
+        <v>Phones in shop, Pieces in shop, Customers, Staff, Coming goods</v>
       </c>
     </row>
     <row r="3">
@@ -1769,32 +2018,32 @@
         <v>Shop</v>
       </c>
       <c r="B3" t="str">
-        <v>Challenge, Ibadan</v>
+        <v>Bodija, Ibadan</v>
       </c>
       <c r="C3" t="str">
-        <v>Phones in shop, Pieces in shop, Staff, Coming goods</v>
+        <v>Phones in shop, Pieces in shop, Customers, Staff, Coming goods</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Tracking</v>
+        <v>Shop</v>
       </c>
       <c r="B4" t="str">
-        <v>IMEI</v>
+        <v>Challenge, Ibadan</v>
       </c>
       <c r="C4" t="str">
-        <v>Items, Coming goods. Phones.</v>
+        <v>Phones in shop, Pieces in shop, Customers, Staff, Coming goods</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Tracking</v>
+        <v>Shop code</v>
       </c>
       <c r="B5" t="str">
-        <v>SERIAL</v>
+        <v>IWO, BOD, CHL</v>
       </c>
       <c r="C5" t="str">
-        <v>Items, Coming goods. Buds or tablets with a serial.</v>
+        <v>Short codes. The shop system reads these too.</v>
       </c>
     </row>
     <row r="6">
@@ -1802,32 +2051,32 @@
         <v>Tracking</v>
       </c>
       <c r="B6" t="str">
-        <v>NONE</v>
+        <v>IMEI</v>
       </c>
       <c r="C6" t="str">
-        <v>Items, Coming goods. Cords and chargers. Use Pieces in shop.</v>
+        <v>Items, Coming goods. Phones.</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Condition</v>
+        <v>Tracking</v>
       </c>
       <c r="B7" t="str">
-        <v>Brand new</v>
+        <v>SERIAL</v>
       </c>
       <c r="C7" t="str">
-        <v>Items, Phones in shop</v>
+        <v>Items, Coming goods. Buds or tablets with a serial.</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Condition</v>
+        <v>Tracking</v>
       </c>
       <c r="B8" t="str">
-        <v>Open box</v>
+        <v>NONE</v>
       </c>
       <c r="C8" t="str">
-        <v>Items, Phones in shop</v>
+        <v>Items, Coming goods. Cords and chargers. Use Pieces in shop.</v>
       </c>
     </row>
     <row r="9">
@@ -1835,7 +2084,7 @@
         <v>Condition</v>
       </c>
       <c r="B9" t="str">
-        <v>UK used</v>
+        <v>Brand new</v>
       </c>
       <c r="C9" t="str">
         <v>Items, Phones in shop</v>
@@ -1846,7 +2095,7 @@
         <v>Condition</v>
       </c>
       <c r="B10" t="str">
-        <v>Refurbished</v>
+        <v>Open box</v>
       </c>
       <c r="C10" t="str">
         <v>Items, Phones in shop</v>
@@ -1857,7 +2106,7 @@
         <v>Condition</v>
       </c>
       <c r="B11" t="str">
-        <v>Swap</v>
+        <v>UK used</v>
       </c>
       <c r="C11" t="str">
         <v>Items, Phones in shop</v>
@@ -1868,7 +2117,7 @@
         <v>Condition</v>
       </c>
       <c r="B12" t="str">
-        <v>Faulty</v>
+        <v>Refurbished</v>
       </c>
       <c r="C12" t="str">
         <v>Items, Phones in shop</v>
@@ -1879,7 +2128,7 @@
         <v>Condition</v>
       </c>
       <c r="B13" t="str">
-        <v>Repair</v>
+        <v>Swap</v>
       </c>
       <c r="C13" t="str">
         <v>Items, Phones in shop</v>
@@ -1887,24 +2136,24 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Grade</v>
+        <v>Condition</v>
       </c>
       <c r="B14" t="str">
-        <v>A</v>
+        <v>Faulty</v>
       </c>
       <c r="C14" t="str">
-        <v>Phones in shop. Like new. Optional.</v>
+        <v>Items, Phones in shop</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Grade</v>
+        <v>Condition</v>
       </c>
       <c r="B15" t="str">
-        <v>B</v>
+        <v>Repair</v>
       </c>
       <c r="C15" t="str">
-        <v>Phones in shop. Light marks. Optional.</v>
+        <v>Items, Phones in shop</v>
       </c>
     </row>
     <row r="16">
@@ -1912,10 +2161,10 @@
         <v>Grade</v>
       </c>
       <c r="B16" t="str">
-        <v>C</v>
+        <v>A</v>
       </c>
       <c r="C16" t="str">
-        <v>Phones in shop. Visible wear. Optional.</v>
+        <v>Phones in shop. Like new. Optional.</v>
       </c>
     </row>
     <row r="17">
@@ -1923,32 +2172,32 @@
         <v>Grade</v>
       </c>
       <c r="B17" t="str">
-        <v>D</v>
+        <v>B</v>
       </c>
       <c r="C17" t="str">
-        <v>Phones in shop. Heavy wear or crack. Optional.</v>
+        <v>Phones in shop. Light marks. Optional.</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Job</v>
+        <v>Grade</v>
       </c>
       <c r="B18" t="str">
-        <v>Super Admin</v>
+        <v>C</v>
       </c>
       <c r="C18" t="str">
-        <v>Staff</v>
+        <v>Phones in shop. Visible wear. Optional.</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Job</v>
+        <v>Grade</v>
       </c>
       <c r="B19" t="str">
-        <v>CEO</v>
+        <v>D</v>
       </c>
       <c r="C19" t="str">
-        <v>Staff</v>
+        <v>Phones in shop. Heavy wear or crack. Optional.</v>
       </c>
     </row>
     <row r="20">
@@ -1956,7 +2205,7 @@
         <v>Job</v>
       </c>
       <c r="B20" t="str">
-        <v>Records checker</v>
+        <v>Super Admin</v>
       </c>
       <c r="C20" t="str">
         <v>Staff</v>
@@ -1967,7 +2216,7 @@
         <v>Job</v>
       </c>
       <c r="B21" t="str">
-        <v>Accountant</v>
+        <v>CEO</v>
       </c>
       <c r="C21" t="str">
         <v>Staff</v>
@@ -1978,7 +2227,7 @@
         <v>Job</v>
       </c>
       <c r="B22" t="str">
-        <v>Shop manager</v>
+        <v>Records checker</v>
       </c>
       <c r="C22" t="str">
         <v>Staff</v>
@@ -1989,7 +2238,7 @@
         <v>Job</v>
       </c>
       <c r="B23" t="str">
-        <v>Goods intake</v>
+        <v>Accountant</v>
       </c>
       <c r="C23" t="str">
         <v>Staff</v>
@@ -2000,7 +2249,7 @@
         <v>Job</v>
       </c>
       <c r="B24" t="str">
-        <v>Cashier</v>
+        <v>Shop manager</v>
       </c>
       <c r="C24" t="str">
         <v>Staff</v>
@@ -2011,7 +2260,7 @@
         <v>Job</v>
       </c>
       <c r="B25" t="str">
-        <v>Sales person</v>
+        <v>Goods intake</v>
       </c>
       <c r="C25" t="str">
         <v>Staff</v>
@@ -2022,38 +2271,71 @@
         <v>Job</v>
       </c>
       <c r="B26" t="str">
-        <v>Repair engineer</v>
+        <v>Stock uploader</v>
       </c>
       <c r="C26" t="str">
-        <v>Staff</v>
+        <v>Staff. Loads this workbook. Cannot sell, see money, or approve.</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>row_type</v>
+        <v>Job</v>
       </c>
       <c r="B27" t="str">
-        <v>SAMPLE</v>
+        <v>Cashier</v>
       </c>
       <c r="C27" t="str">
-        <v>Every data tab. Delete these rows before you send, or we will ignore them.</v>
+        <v>Staff</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
+        <v>Job</v>
+      </c>
+      <c r="B28" t="str">
+        <v>Sales person</v>
+      </c>
+      <c r="C28" t="str">
+        <v>Staff</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>Job</v>
+      </c>
+      <c r="B29" t="str">
+        <v>Repair engineer</v>
+      </c>
+      <c r="C29" t="str">
+        <v>Staff</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
         <v>row_type</v>
       </c>
-      <c r="B28" t="str">
+      <c r="B30" t="str">
+        <v>SAMPLE</v>
+      </c>
+      <c r="C30" t="str">
+        <v>Every data tab. Delete these rows, or leave them. The shop system never loads a row marked SAMPLE.</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>row_type</v>
+      </c>
+      <c r="B31" t="str">
         <v>REAL</v>
       </c>
-      <c r="C28" t="str">
+      <c r="C31" t="str">
         <v>Every data tab. Your live rows.</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C28"/>
+  <autoFilter ref="A1:C31"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C28"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C31"/>
   </ignoredErrors>
 </worksheet>
 </file>